--- a/data/trans_dic/IP31KM06_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 54,8</t>
+          <t>35,88; 60,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,37; 57,8</t>
+          <t>33,22; 57,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,38; 52,18</t>
+          <t>36,65; 55,24</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 48,23</t>
+          <t>34,6; 44,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,5; 45,16</t>
+          <t>30,21; 38,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,98; 44,22</t>
+          <t>33,86; 40,11</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,55; 37,38</t>
+          <t>27,23; 39,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,87; 40,21</t>
+          <t>25,74; 39,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,98; 37,17</t>
+          <t>28,31; 37,21</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,94; 44,05</t>
+          <t>35,12; 42,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,3</t>
+          <t>31,09; 37,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,21; 40,94</t>
+          <t>34,22; 39,29</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>45876</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12477; 29429</t>
+          <t>19273; 32398</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20056; 33724</t>
+          <t>15252; 26473</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36279; 58465</t>
+          <t>36514; 55027</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>200</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>163305</t>
+          <t>184981</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>197538</t>
+          <t>143574</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360843</t>
+          <t>328555</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138242; 217919</t>
+          <t>161377; 208360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>174327; 228170</t>
+          <t>128291; 163452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>325216; 423255</t>
+          <t>301736; 357432</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45392</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60460</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105852</t>
+          <t>101954</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35886; 54643</t>
+          <t>45394; 66016</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48674; 72841</t>
+          <t>37880; 57516</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91575; 121657</t>
+          <t>88855; 116781</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>290</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>230130</t>
+          <t>265182</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>201649; 287090</t>
+          <t>241225; 291196</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254866; 315021</t>
+          <t>192073; 234244</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>477698; 571729</t>
+          <t>446387; 512491</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM06_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>35,88; 60,31</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33,22; 57,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36,65; 55,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>39,66%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>33,81%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>34,6; 44,67</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30,21; 38,49</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33,86; 40,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>32,08%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,23; 39,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>25,74; 39,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28,31; 37,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>35,12; 42,4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31,09; 37,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34,22; 39,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4737700023465548</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4449967426420227</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4605112515095257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>25449</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20428</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45876</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3587987365198446</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3322484191843197</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.36653685571497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19273; 32398</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15252; 26473</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36514; 55027</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6031458928168438</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5766895981494412</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5523685859319125</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3965942799740929</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3380858972726525</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3687109556249882</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>184981</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>143574</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>328555</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.3459876240729632</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3020994592962929</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.3386150225665748</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>161377; 208360</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>128291; 163452</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>301736; 357432</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4467191618895073</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3848951379263127</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4011180114540963</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3284791461565829</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.320790621085503</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3248743144772246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>54753</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>47201</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101954</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2723319887408391</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2574420517137329</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2831340151634217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>45394; 66016</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37880; 57516</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>88855; 116781</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3960482748252773</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3908951220412429</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3721225028985887</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3860990997494866</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3419111452083629</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3651756362221145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>265182</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>211202</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>476384</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3512185179999625</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3109430554143286</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3421811226636931</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>241225; 291196</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>192073; 234244</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>446387; 512491</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4239741178621034</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.379213523141195</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3928534540412045</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>25449</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>20428</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>45876</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>19273</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>15252</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>36514</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>32398</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>26473</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>55027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>184981</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>143574</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>328555</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>161377</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>128291</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>301736</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>208360</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>163452</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>357432</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>54753</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>47201</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>101954</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>45394</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>37880</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>88855</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>66016</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>57516</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>116781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>265182</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>211202</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>476384</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>241225</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>192073</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>446387</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>291196</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>234244</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>512491</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>